--- a/Utms-Generator/clients/SFG.xlsx
+++ b/Utms-Generator/clients/SFG.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approved UTMs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Approved UTMs'!$A$1:$I$856</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Approved UTMs'!$A$1:$I$876</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -137,8 +137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ApprovedUTMs" displayName="ApprovedUTMs" ref="A1:I856" headerRowCount="1">
-  <autoFilter ref="A1:I856"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ApprovedUTMs" displayName="ApprovedUTMs" ref="A1:I876" headerRowCount="1">
+  <autoFilter ref="A1:I876"/>
   <tableColumns count="9">
     <tableColumn id="1" name="client"/>
     <tableColumn id="2" name="destination_url"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I856"/>
+  <dimension ref="A1:I876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19832,7 +19832,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -19918,7 +19918,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G465" t="inlineStr"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G469" t="inlineStr"/>
@@ -20168,7 +20168,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -20188,7 +20188,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G473" t="inlineStr"/>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -20485,7 +20485,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G477" t="inlineStr"/>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -20547,7 +20547,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -20567,7 +20567,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
+          <t>https://studleys.com/product-category/houseplants/patio/</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>ScentedGeranium</t>
+          <t>Patio</t>
         </is>
       </c>
       <c r="G481" t="inlineStr"/>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -20715,7 +20715,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -20758,7 +20758,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G485" t="inlineStr"/>
@@ -20840,7 +20840,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -20903,7 +20903,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -20989,7 +20989,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G489" t="inlineStr"/>
@@ -21008,7 +21008,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -21028,7 +21028,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -21071,7 +21071,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G493" t="inlineStr"/>
@@ -21176,7 +21176,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -21196,7 +21196,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -21239,7 +21239,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -21282,7 +21282,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -21305,7 +21305,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -21325,7 +21325,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G497" t="inlineStr"/>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -21387,7 +21387,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/succulent/</t>
+          <t>https://studleys.com/product-category/houseplants/scented-geranium/</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Succulent</t>
+          <t>ScentedGeranium</t>
         </is>
       </c>
       <c r="G501" t="inlineStr"/>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G505" t="inlineStr"/>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -21723,7 +21723,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -21743,7 +21743,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -21829,7 +21829,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G509" t="inlineStr"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -21868,7 +21868,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -21891,7 +21891,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -21911,7 +21911,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -21934,7 +21934,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -21977,7 +21977,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -21997,7 +21997,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G513" t="inlineStr"/>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -22059,7 +22059,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -22079,7 +22079,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -22102,7 +22102,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -22122,7 +22122,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -22145,7 +22145,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G517" t="inlineStr"/>
@@ -22184,7 +22184,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -22227,7 +22227,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -22247,7 +22247,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -22270,7 +22270,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
+          <t>https://studleys.com/product-category/houseplants/succulent/</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Terrarium</t>
+          <t>Succulent</t>
         </is>
       </c>
       <c r="G521" t="inlineStr"/>
@@ -22352,7 +22352,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -22481,7 +22481,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -22501,7 +22501,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G525" t="inlineStr"/>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -22540,7 +22540,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22583,7 +22583,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -22606,7 +22606,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -22669,7 +22669,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G529" t="inlineStr"/>
@@ -22688,7 +22688,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -22708,7 +22708,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -22751,7 +22751,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -22774,7 +22774,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -22837,7 +22837,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G533" t="inlineStr"/>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -22919,7 +22919,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -22942,7 +22942,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G537" t="inlineStr"/>
@@ -23024,7 +23024,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -23153,7 +23153,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/trailing/</t>
+          <t>https://studleys.com/product-category/houseplants/terrarium/</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -23173,7 +23173,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Trailing</t>
+          <t>Terrarium</t>
         </is>
       </c>
       <c r="G541" t="inlineStr"/>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -23212,7 +23212,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -23235,7 +23235,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -23255,7 +23255,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
@@ -23278,7 +23278,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G545" t="inlineStr"/>
@@ -23360,7 +23360,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -23380,7 +23380,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -23509,7 +23509,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G549" t="inlineStr"/>
@@ -23528,7 +23528,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -23548,7 +23548,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -23571,7 +23571,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -23614,7 +23614,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -23634,7 +23634,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G553" t="inlineStr"/>
@@ -23696,7 +23696,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -23739,7 +23739,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -23759,7 +23759,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -23782,7 +23782,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G557" t="inlineStr"/>
@@ -23864,7 +23864,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23927,7 +23927,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23970,7 +23970,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
+          <t>https://studleys.com/product-category/houseplants/trailing/</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -24013,7 +24013,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Windowsill</t>
+          <t>Trailing</t>
         </is>
       </c>
       <c r="G561" t="inlineStr"/>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -24052,7 +24052,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -24075,7 +24075,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -24118,7 +24118,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -24138,7 +24138,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G565" t="inlineStr"/>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -24220,7 +24220,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -24243,7 +24243,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -24306,7 +24306,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
@@ -24329,7 +24329,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G569" t="inlineStr"/>
@@ -24368,7 +24368,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -24411,7 +24411,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -24431,7 +24431,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -24474,7 +24474,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -24497,7 +24497,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G573" t="inlineStr"/>
@@ -24536,7 +24536,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -24622,7 +24622,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -24665,7 +24665,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24685,7 +24685,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G577" t="inlineStr"/>
@@ -24704,7 +24704,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -24747,7 +24747,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -24810,7 +24810,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -24833,7 +24833,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/blooming/</t>
+          <t>https://studleys.com/product-category/houseplants/windowsill/</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Windowsill</t>
         </is>
       </c>
       <c r="G581" t="inlineStr"/>
@@ -24872,7 +24872,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -24915,7 +24915,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
@@ -24958,7 +24958,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -24978,7 +24978,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G585" t="inlineStr"/>
@@ -25040,7 +25040,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -25103,7 +25103,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -25126,7 +25126,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -25146,7 +25146,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -25169,7 +25169,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -25189,7 +25189,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G589" t="inlineStr"/>
@@ -25208,7 +25208,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -25228,7 +25228,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -25251,7 +25251,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
@@ -25294,7 +25294,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -25314,7 +25314,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -25337,7 +25337,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -25357,7 +25357,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G593" t="inlineStr"/>
@@ -25376,7 +25376,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -25396,7 +25396,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
@@ -25419,7 +25419,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -25439,7 +25439,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
@@ -25462,7 +25462,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -25482,7 +25482,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
@@ -25505,7 +25505,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -25525,7 +25525,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G597" t="inlineStr"/>
@@ -25544,7 +25544,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -25607,7 +25607,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -25650,7 +25650,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -25673,7 +25673,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
+          <t>https://studleys.com/product-category/houseplants/blooming/</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>AirPurifying</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G601" t="inlineStr"/>
@@ -25712,7 +25712,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -25755,7 +25755,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -25818,7 +25818,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -25861,7 +25861,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G605" t="inlineStr"/>
@@ -25880,7 +25880,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -25900,7 +25900,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -25923,7 +25923,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -25943,7 +25943,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -25966,7 +25966,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -26009,7 +26009,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G609" t="inlineStr"/>
@@ -26048,7 +26048,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -26068,7 +26068,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -26091,7 +26091,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -26111,7 +26111,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -26134,7 +26134,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -26197,7 +26197,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G613" t="inlineStr"/>
@@ -26216,7 +26216,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -26236,7 +26236,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -26259,7 +26259,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -26279,7 +26279,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -26302,7 +26302,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -26345,7 +26345,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -26365,7 +26365,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G617" t="inlineStr"/>
@@ -26384,7 +26384,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -26427,7 +26427,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -26490,7 +26490,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -26513,7 +26513,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
+          <t>https://studleys.com/product-category/houseplants/air-purifying/</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -26533,7 +26533,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Bonsai</t>
+          <t>AirPurifying</t>
         </is>
       </c>
       <c r="G621" t="inlineStr"/>
@@ -26552,7 +26552,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -26567,17 +26567,17 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="H622" t="inlineStr"/>
@@ -26595,7 +26595,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -26610,12 +26610,12 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -26638,7 +26638,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -26653,12 +26653,12 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -26696,12 +26696,12 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G625" t="inlineStr"/>
@@ -26720,7 +26720,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -26735,17 +26735,17 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="H626" t="inlineStr"/>
@@ -26763,7 +26763,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -26778,12 +26778,12 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -26806,7 +26806,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -26821,12 +26821,12 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -26849,7 +26849,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -26864,12 +26864,12 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G629" t="inlineStr"/>
@@ -26888,7 +26888,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -26903,17 +26903,17 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="H630" t="inlineStr"/>
@@ -26931,7 +26931,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -26946,12 +26946,12 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -26974,7 +26974,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -26989,12 +26989,12 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -27032,12 +27032,12 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G633" t="inlineStr"/>
@@ -27056,7 +27056,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -27071,17 +27071,17 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="H634" t="inlineStr"/>
@@ -27099,7 +27099,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -27114,12 +27114,12 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -27142,7 +27142,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -27157,12 +27157,12 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -27185,7 +27185,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -27200,12 +27200,12 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G637" t="inlineStr"/>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -27239,17 +27239,17 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="H638" t="inlineStr"/>
@@ -27267,7 +27267,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -27282,12 +27282,12 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -27310,7 +27310,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -27325,12 +27325,12 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -27353,7 +27353,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>https://studleys.com/garden-plants/</t>
+          <t>https://studleys.com/product-category/houseplants/bonsai/</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -27368,12 +27368,12 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>GardenCenter</t>
+          <t>Houseplants</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Bonsai</t>
         </is>
       </c>
       <c r="G641" t="inlineStr"/>
@@ -27392,7 +27392,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -27407,7 +27407,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
@@ -27478,7 +27478,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -27493,7 +27493,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
@@ -27521,7 +27521,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -27536,7 +27536,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
@@ -27560,7 +27560,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -27575,7 +27575,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
@@ -27603,7 +27603,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -27618,7 +27618,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
@@ -27646,7 +27646,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -27728,7 +27728,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -27743,7 +27743,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
@@ -27771,7 +27771,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -27786,7 +27786,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
@@ -27857,7 +27857,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -27911,7 +27911,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -27954,7 +27954,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
@@ -27982,7 +27982,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -28122,7 +28122,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -28150,7 +28150,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -28165,7 +28165,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>https://studleys.com/wedding-flowers/</t>
+          <t>https://studleys.com/garden-plants/</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -28208,7 +28208,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Wedding</t>
+          <t>GardenCenter</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
@@ -28232,7 +28232,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -28252,7 +28252,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -28295,7 +28295,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -28318,7 +28318,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -28361,7 +28361,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -28381,7 +28381,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G665" t="inlineStr"/>
@@ -28400,7 +28400,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -28420,7 +28420,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -28443,7 +28443,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -28463,7 +28463,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -28486,7 +28486,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -28506,7 +28506,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -28549,7 +28549,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G669" t="inlineStr"/>
@@ -28568,7 +28568,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -28611,7 +28611,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -28631,7 +28631,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -28697,7 +28697,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -28717,7 +28717,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G673" t="inlineStr"/>
@@ -28736,7 +28736,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -28756,7 +28756,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -28779,7 +28779,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -28799,7 +28799,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -28842,7 +28842,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -28865,7 +28865,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -28885,7 +28885,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G677" t="inlineStr"/>
@@ -28904,7 +28904,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -28947,7 +28947,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -28990,7 +28990,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -29010,7 +29010,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>https://studleys.com/diy-wedding-flowers/</t>
+          <t>https://studleys.com/wedding-flowers/</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -29053,7 +29053,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>DIYWedding</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G681" t="inlineStr"/>
@@ -29072,7 +29072,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -29087,12 +29087,12 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -29115,7 +29115,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -29173,12 +29173,12 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -29201,7 +29201,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -29216,12 +29216,12 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G685" t="inlineStr"/>
@@ -29240,7 +29240,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -29255,12 +29255,12 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -29283,7 +29283,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -29298,12 +29298,12 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -29326,7 +29326,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -29341,12 +29341,12 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -29384,12 +29384,12 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G689" t="inlineStr"/>
@@ -29408,7 +29408,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -29423,12 +29423,12 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -29466,12 +29466,12 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -29494,7 +29494,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -29509,12 +29509,12 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -29537,7 +29537,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -29552,12 +29552,12 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G693" t="inlineStr"/>
@@ -29576,7 +29576,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -29591,12 +29591,12 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -29619,7 +29619,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -29634,12 +29634,12 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -29662,7 +29662,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -29677,12 +29677,12 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -29705,7 +29705,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -29720,12 +29720,12 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G697" t="inlineStr"/>
@@ -29744,7 +29744,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -29759,12 +29759,12 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -29802,12 +29802,12 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -29830,7 +29830,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -29845,12 +29845,12 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -29873,7 +29873,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>https://studleys.com/landscaping/</t>
+          <t>https://studleys.com/diy-wedding-flowers/</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -29888,12 +29888,12 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Wedding</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>DIYWedding</t>
         </is>
       </c>
       <c r="G701" t="inlineStr"/>
@@ -29912,7 +29912,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29932,7 +29932,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29975,7 +29975,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -29998,7 +29998,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -30018,7 +30018,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -30041,7 +30041,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -30061,7 +30061,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G705" t="inlineStr"/>
@@ -30080,7 +30080,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -30100,7 +30100,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -30123,7 +30123,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -30143,7 +30143,7 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -30166,7 +30166,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -30186,7 +30186,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -30209,7 +30209,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -30229,7 +30229,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G709" t="inlineStr"/>
@@ -30248,7 +30248,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -30268,7 +30268,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -30291,7 +30291,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -30311,7 +30311,7 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -30354,7 +30354,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -30377,7 +30377,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -30397,7 +30397,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G713" t="inlineStr"/>
@@ -30416,7 +30416,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -30459,7 +30459,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -30479,7 +30479,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -30502,7 +30502,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -30522,7 +30522,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -30545,7 +30545,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G717" t="inlineStr"/>
@@ -30584,7 +30584,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -30627,7 +30627,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -30647,7 +30647,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -30670,7 +30670,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -30713,7 +30713,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>https://studleys.com/irrigation-services/</t>
+          <t>https://studleys.com/landscaping/</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -30733,7 +30733,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>IrrigationServices</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G721" t="inlineStr"/>
@@ -30752,7 +30752,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -30767,12 +30767,12 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -30795,7 +30795,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -30810,12 +30810,12 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -30853,12 +30853,12 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -30881,7 +30881,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -30896,12 +30896,12 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G725" t="inlineStr"/>
@@ -30920,7 +30920,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -30935,12 +30935,12 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -30963,7 +30963,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -31006,7 +31006,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -31021,12 +31021,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -31064,12 +31064,12 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G729" t="inlineStr"/>
@@ -31088,7 +31088,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -31103,12 +31103,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -31131,7 +31131,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -31174,7 +31174,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -31189,12 +31189,12 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -31217,7 +31217,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -31232,12 +31232,12 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G733" t="inlineStr"/>
@@ -31256,7 +31256,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -31271,12 +31271,12 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -31299,7 +31299,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -31314,12 +31314,12 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -31342,7 +31342,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -31357,12 +31357,12 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -31385,7 +31385,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -31400,12 +31400,12 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G737" t="inlineStr"/>
@@ -31424,7 +31424,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -31439,12 +31439,12 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -31467,7 +31467,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -31482,12 +31482,12 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -31510,7 +31510,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -31525,12 +31525,12 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -31553,7 +31553,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>https://studleys.com/about/</t>
+          <t>https://studleys.com/irrigation-services/</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -31568,12 +31568,12 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Landscaping</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>IrrigationServices</t>
         </is>
       </c>
       <c r="G741" t="inlineStr"/>
@@ -31592,7 +31592,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -31612,7 +31612,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -31678,7 +31678,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -31698,7 +31698,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -31721,7 +31721,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G745" t="inlineStr"/>
@@ -31760,7 +31760,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -31803,7 +31803,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -31823,7 +31823,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -31889,7 +31889,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -31909,7 +31909,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G749" t="inlineStr"/>
@@ -31928,7 +31928,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -31971,7 +31971,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -31991,7 +31991,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -32014,7 +32014,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -32034,7 +32034,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -32057,7 +32057,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -32077,7 +32077,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G753" t="inlineStr"/>
@@ -32096,7 +32096,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -32116,7 +32116,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -32139,7 +32139,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -32159,7 +32159,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -32182,7 +32182,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -32202,7 +32202,7 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -32225,7 +32225,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -32245,7 +32245,7 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G757" t="inlineStr"/>
@@ -32264,7 +32264,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -32307,7 +32307,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -32327,7 +32327,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -32350,7 +32350,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -32370,7 +32370,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -32393,7 +32393,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>https://studleys.com/studleys-guarantee/</t>
+          <t>https://studleys.com/about/</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -32413,7 +32413,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>Guarantee</t>
+          <t>LandingPage</t>
         </is>
       </c>
       <c r="G761" t="inlineStr"/>
@@ -32432,7 +32432,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -32495,7 +32495,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -32518,7 +32518,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -32538,7 +32538,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -32561,7 +32561,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -32581,7 +32581,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G765" t="inlineStr"/>
@@ -32600,7 +32600,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -32620,7 +32620,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -32643,7 +32643,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -32663,7 +32663,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -32686,7 +32686,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -32706,7 +32706,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -32729,7 +32729,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -32749,7 +32749,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G769" t="inlineStr"/>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -32788,7 +32788,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -32811,7 +32811,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -32831,7 +32831,7 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -32854,7 +32854,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -32874,7 +32874,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -32897,7 +32897,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -32917,7 +32917,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G773" t="inlineStr"/>
@@ -32936,7 +32936,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -32956,7 +32956,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
@@ -32979,7 +32979,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -32999,7 +32999,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -33022,7 +33022,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -33042,7 +33042,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
@@ -33065,7 +33065,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -33085,7 +33085,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G777" t="inlineStr"/>
@@ -33104,7 +33104,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
@@ -33147,7 +33147,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -33167,7 +33167,7 @@
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
@@ -33190,7 +33190,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -33210,7 +33210,7 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
@@ -33233,7 +33233,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>https://studleys.com/faq/</t>
+          <t>https://studleys.com/studleys-guarantee/</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -33253,7 +33253,7 @@
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>Guarantee</t>
         </is>
       </c>
       <c r="G781" t="inlineStr"/>
@@ -33272,7 +33272,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -33292,7 +33292,7 @@
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
@@ -33315,7 +33315,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
@@ -33358,7 +33358,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -33378,7 +33378,7 @@
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
@@ -33401,7 +33401,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -33421,7 +33421,7 @@
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G785" t="inlineStr"/>
@@ -33440,7 +33440,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -33460,7 +33460,7 @@
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
@@ -33483,7 +33483,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -33503,7 +33503,7 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
@@ -33526,7 +33526,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
@@ -33569,7 +33569,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
@@ -33589,7 +33589,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G789" t="inlineStr"/>
@@ -33608,7 +33608,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
@@ -33628,7 +33628,7 @@
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
@@ -33651,7 +33651,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
@@ -33694,7 +33694,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
@@ -33714,7 +33714,7 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -33757,7 +33757,7 @@
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G793" t="inlineStr"/>
@@ -33776,7 +33776,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -33796,7 +33796,7 @@
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
@@ -33819,7 +33819,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -33839,7 +33839,7 @@
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G795" t="inlineStr">
@@ -33862,7 +33862,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
@@ -33905,7 +33905,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G797" t="inlineStr"/>
@@ -33944,7 +33944,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
@@ -33987,7 +33987,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -34007,7 +34007,7 @@
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
@@ -34030,7 +34030,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -34050,7 +34050,7 @@
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>https://studleys.com/refunds-returns/</t>
+          <t>https://studleys.com/faq/</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -34093,7 +34093,7 @@
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>RefundsReturns</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="G801" t="inlineStr"/>
@@ -34112,7 +34112,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -34132,12 +34132,12 @@
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="H802" t="inlineStr"/>
@@ -34155,7 +34155,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -34175,12 +34175,12 @@
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Learn</t>
         </is>
       </c>
       <c r="H803" t="inlineStr"/>
@@ -34198,7 +34198,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -34218,10 +34218,14 @@
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>Donations</t>
-        </is>
-      </c>
-      <c r="G804" t="inlineStr"/>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>Explore</t>
+        </is>
+      </c>
       <c r="H804" t="inlineStr"/>
       <c r="I804" t="inlineStr">
         <is>
@@ -34237,12 +34241,12 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D805" t="inlineStr">
@@ -34257,14 +34261,10 @@
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>Donations</t>
-        </is>
-      </c>
-      <c r="G805" t="inlineStr">
-        <is>
-          <t>Request</t>
-        </is>
-      </c>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr"/>
       <c r="H805" t="inlineStr"/>
       <c r="I805" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -34300,12 +34300,12 @@
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="H806" t="inlineStr"/>
@@ -34323,7 +34323,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -34343,10 +34343,14 @@
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>Donations</t>
-        </is>
-      </c>
-      <c r="G807" t="inlineStr"/>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
       <c r="H807" t="inlineStr"/>
       <c r="I807" t="inlineStr">
         <is>
@@ -34362,12 +34366,12 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -34382,12 +34386,12 @@
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="H808" t="inlineStr"/>
@@ -34405,12 +34409,12 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
@@ -34425,14 +34429,10 @@
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>Donations</t>
-        </is>
-      </c>
-      <c r="G809" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr"/>
       <c r="H809" t="inlineStr"/>
       <c r="I809" t="inlineStr">
         <is>
@@ -34448,7 +34448,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -34468,10 +34468,14 @@
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>Donations</t>
-        </is>
-      </c>
-      <c r="G810" t="inlineStr"/>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
       <c r="H810" t="inlineStr"/>
       <c r="I810" t="inlineStr">
         <is>
@@ -34487,12 +34491,12 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -34507,12 +34511,12 @@
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Learn</t>
         </is>
       </c>
       <c r="H811" t="inlineStr"/>
@@ -34530,12 +34534,12 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -34550,12 +34554,12 @@
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="H812" t="inlineStr"/>
@@ -34573,12 +34577,12 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -34593,7 +34597,7 @@
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G813" t="inlineStr"/>
@@ -34612,17 +34616,17 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
@@ -34632,12 +34636,12 @@
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>Request</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="H814" t="inlineStr"/>
@@ -34655,17 +34659,17 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E815" t="inlineStr">
@@ -34675,12 +34679,12 @@
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Learn</t>
         </is>
       </c>
       <c r="H815" t="inlineStr"/>
@@ -34698,17 +34702,17 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>https://studleys.com/donations/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -34718,10 +34722,14 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>Donations</t>
-        </is>
-      </c>
-      <c r="G816" t="inlineStr"/>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>Explore</t>
+        </is>
+      </c>
       <c r="H816" t="inlineStr"/>
       <c r="I816" t="inlineStr">
         <is>
@@ -34737,12 +34745,12 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -34757,14 +34765,10 @@
       </c>
       <c r="F817" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>SignUp</t>
-        </is>
-      </c>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr"/>
       <c r="H817" t="inlineStr"/>
       <c r="I817" t="inlineStr">
         <is>
@@ -34780,17 +34784,17 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E818" t="inlineStr">
@@ -34800,12 +34804,12 @@
       </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>Subscribe</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="H818" t="inlineStr"/>
@@ -34823,17 +34827,17 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
@@ -34843,10 +34847,14 @@
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G819" t="inlineStr"/>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>Learn</t>
+        </is>
+      </c>
       <c r="H819" t="inlineStr"/>
       <c r="I819" t="inlineStr">
         <is>
@@ -34862,17 +34870,17 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E820" t="inlineStr">
@@ -34882,12 +34890,12 @@
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
+          <t>RefundsReturns</t>
         </is>
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>SignUp</t>
+          <t>Explore</t>
         </is>
       </c>
       <c r="H820" t="inlineStr"/>
@@ -34905,17 +34913,17 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/refunds-returns/</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E821" t="inlineStr">
@@ -34925,14 +34933,10 @@
       </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G821" t="inlineStr">
-        <is>
-          <t>Subscribe</t>
-        </is>
-      </c>
+          <t>RefundsReturns</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr"/>
       <c r="H821" t="inlineStr"/>
       <c r="I821" t="inlineStr">
         <is>
@@ -34948,12 +34952,12 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D822" t="inlineStr">
@@ -34968,10 +34972,14 @@
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G822" t="inlineStr"/>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
       <c r="H822" t="inlineStr"/>
       <c r="I822" t="inlineStr">
         <is>
@@ -34987,12 +34995,12 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -35007,12 +35015,12 @@
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>SignUp</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="H823" t="inlineStr"/>
@@ -35030,12 +35038,12 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -35050,14 +35058,10 @@
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G824" t="inlineStr">
-        <is>
-          <t>Subscribe</t>
-        </is>
-      </c>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr"/>
       <c r="H824" t="inlineStr"/>
       <c r="I824" t="inlineStr">
         <is>
@@ -35073,12 +35077,12 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -35093,10 +35097,14 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G825" t="inlineStr"/>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
       <c r="H825" t="inlineStr"/>
       <c r="I825" t="inlineStr">
         <is>
@@ -35112,12 +35120,12 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -35132,12 +35140,12 @@
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>SignUp</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="H826" t="inlineStr"/>
@@ -35155,12 +35163,12 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -35175,14 +35183,10 @@
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G827" t="inlineStr">
-        <is>
-          <t>Subscribe</t>
-        </is>
-      </c>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr"/>
       <c r="H827" t="inlineStr"/>
       <c r="I827" t="inlineStr">
         <is>
@@ -35198,12 +35202,12 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -35218,10 +35222,14 @@
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G828" t="inlineStr"/>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
       <c r="H828" t="inlineStr"/>
       <c r="I828" t="inlineStr">
         <is>
@@ -35237,17 +35245,17 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
@@ -35257,12 +35265,12 @@
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>SignUp</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="H829" t="inlineStr"/>
@@ -35280,17 +35288,17 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
@@ -35300,14 +35308,10 @@
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G830" t="inlineStr">
-        <is>
-          <t>Subscribe</t>
-        </is>
-      </c>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr"/>
       <c r="H830" t="inlineStr"/>
       <c r="I830" t="inlineStr">
         <is>
@@ -35323,17 +35327,17 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>https://studleys.com/enews/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E831" t="inlineStr">
@@ -35343,10 +35347,14 @@
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>SignUpEnews</t>
-        </is>
-      </c>
-      <c r="G831" t="inlineStr"/>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
       <c r="H831" t="inlineStr"/>
       <c r="I831" t="inlineStr">
         <is>
@@ -35362,12 +35370,12 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
@@ -35377,12 +35385,12 @@
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G832" t="inlineStr">
@@ -35405,12 +35413,12 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -35420,12 +35428,12 @@
       </c>
       <c r="E833" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G833" t="inlineStr"/>
@@ -35444,32 +35452,32 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G834" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Request</t>
         </is>
       </c>
       <c r="H834" t="inlineStr"/>
@@ -35487,30 +35495,34 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
         <is>
+          <t>About</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
           <t>Contact</t>
         </is>
       </c>
-      <c r="F835" t="inlineStr">
-        <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G835" t="inlineStr"/>
       <c r="H835" t="inlineStr"/>
       <c r="I835" t="inlineStr">
         <is>
@@ -35526,34 +35538,30 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/donations/</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G836" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr"/>
       <c r="H836" t="inlineStr"/>
       <c r="I836" t="inlineStr">
         <is>
@@ -35569,12 +35577,12 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D837" t="inlineStr">
@@ -35584,15 +35592,19 @@
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G837" t="inlineStr"/>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>SignUp</t>
+        </is>
+      </c>
       <c r="H837" t="inlineStr"/>
       <c r="I837" t="inlineStr">
         <is>
@@ -35608,12 +35620,12 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
@@ -35623,17 +35635,17 @@
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>SignUpEnews</t>
         </is>
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Subscribe</t>
         </is>
       </c>
       <c r="H838" t="inlineStr"/>
@@ -35651,12 +35663,12 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
@@ -35666,12 +35678,12 @@
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>SignUpEnews</t>
         </is>
       </c>
       <c r="G839" t="inlineStr"/>
@@ -35690,32 +35702,32 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>SignUpEnews</t>
         </is>
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>SignUp</t>
         </is>
       </c>
       <c r="H840" t="inlineStr"/>
@@ -35733,30 +35745,34 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>https://studleys.com/contact-us/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G841" t="inlineStr"/>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>Subscribe</t>
+        </is>
+      </c>
       <c r="H841" t="inlineStr"/>
       <c r="I841" t="inlineStr">
         <is>
@@ -35772,12 +35788,12 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
@@ -35787,19 +35803,15 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G842" t="inlineStr">
-        <is>
-          <t>SignIn</t>
-        </is>
-      </c>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr"/>
       <c r="H842" t="inlineStr"/>
       <c r="I842" t="inlineStr">
         <is>
@@ -35815,12 +35827,12 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
@@ -35830,17 +35842,17 @@
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>SignUpEnews</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>SignUp</t>
         </is>
       </c>
       <c r="H843" t="inlineStr"/>
@@ -35858,12 +35870,12 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
@@ -35873,15 +35885,19 @@
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G844" t="inlineStr"/>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>Subscribe</t>
+        </is>
+      </c>
       <c r="H844" t="inlineStr"/>
       <c r="I844" t="inlineStr">
         <is>
@@ -35897,12 +35913,12 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
@@ -35912,19 +35928,15 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G845" t="inlineStr">
-        <is>
-          <t>SignIn</t>
-        </is>
-      </c>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr"/>
       <c r="H845" t="inlineStr"/>
       <c r="I845" t="inlineStr">
         <is>
@@ -35940,12 +35952,12 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
@@ -35955,17 +35967,17 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>SignUpEnews</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>SignUp</t>
         </is>
       </c>
       <c r="H846" t="inlineStr"/>
@@ -35983,12 +35995,12 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
@@ -35998,15 +36010,19 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G847" t="inlineStr"/>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>Subscribe</t>
+        </is>
+      </c>
       <c r="H847" t="inlineStr"/>
       <c r="I847" t="inlineStr">
         <is>
@@ -36022,12 +36038,12 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
@@ -36037,19 +36053,15 @@
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G848" t="inlineStr">
-        <is>
-          <t>SignIn</t>
-        </is>
-      </c>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr"/>
       <c r="H848" t="inlineStr"/>
       <c r="I848" t="inlineStr">
         <is>
@@ -36065,32 +36077,32 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>LandingPage</t>
+          <t>SignUpEnews</t>
         </is>
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>SignUp</t>
         </is>
       </c>
       <c r="H849" t="inlineStr"/>
@@ -36108,30 +36120,34 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G850" t="inlineStr"/>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>Subscribe</t>
+        </is>
+      </c>
       <c r="H850" t="inlineStr"/>
       <c r="I850" t="inlineStr">
         <is>
@@ -36147,34 +36163,30 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/enews/</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>ConstantContact</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>About</t>
         </is>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>LandingPage</t>
-        </is>
-      </c>
-      <c r="G851" t="inlineStr">
-        <is>
-          <t>SignIn</t>
-        </is>
-      </c>
+          <t>SignUpEnews</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr"/>
       <c r="H851" t="inlineStr"/>
       <c r="I851" t="inlineStr">
         <is>
@@ -36190,12 +36202,12 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/contact-us/</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -36205,7 +36217,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
@@ -36215,7 +36227,7 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>Register</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="H852" t="inlineStr"/>
@@ -36233,12 +36245,12 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/contact-us/</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
@@ -36248,7 +36260,7 @@
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
@@ -36272,22 +36284,22 @@
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/contact-us/</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
@@ -36297,7 +36309,7 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>SignIn</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="H854" t="inlineStr"/>
@@ -36315,22 +36327,22 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/contact-us/</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
@@ -36338,11 +36350,7 @@
           <t>LandingPage</t>
         </is>
       </c>
-      <c r="G855" t="inlineStr">
-        <is>
-          <t>Register</t>
-        </is>
-      </c>
+      <c r="G855" t="inlineStr"/>
       <c r="H855" t="inlineStr"/>
       <c r="I855" t="inlineStr">
         <is>
@@ -36358,22 +36366,22 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>https://studleys.com/my-account/</t>
+          <t>https://studleys.com/contact-us/</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>ConstantContact</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>MyAccount</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
@@ -36381,7 +36389,11 @@
           <t>LandingPage</t>
         </is>
       </c>
-      <c r="G856" t="inlineStr"/>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
       <c r="H856" t="inlineStr"/>
       <c r="I856" t="inlineStr">
         <is>
@@ -36389,8 +36401,836 @@
         </is>
       </c>
     </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>https://studleys.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr"/>
+      <c r="H857" t="inlineStr"/>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>https://studleys.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr"/>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>https://studleys.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr"/>
+      <c r="H859" t="inlineStr"/>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>https://studleys.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>ConstantContact</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>https://studleys.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>ConstantContact</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr"/>
+      <c r="H861" t="inlineStr"/>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>SignIn</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr"/>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr"/>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr"/>
+      <c r="H864" t="inlineStr"/>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>SignIn</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr"/>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr"/>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>GMB</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr"/>
+      <c r="H867" t="inlineStr"/>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>SignIn</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr"/>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr"/>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr"/>
+      <c r="H870" t="inlineStr"/>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>SignIn</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr"/>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr"/>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr"/>
+      <c r="H873" t="inlineStr"/>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>ConstantContact</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>SignIn</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr"/>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>ConstantContact</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr"/>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>https://studleys.com/my-account/</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>ConstantContact</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>MyAccount</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>LandingPage</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr"/>
+      <c r="H876" t="inlineStr"/>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I856"/>
+  <autoFilter ref="A1:I876"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
